--- a/data/raw/ind_nss2223_hdds.xlsx
+++ b/data/raw/ind_nss2223_hdds.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/gabriel_battcock_wfp_org/Documents/Documents/MIMI_mac/nsso_hces_2023/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/gabriel_battcock_wfp_org/Documents/Documents/MIMI_mac/nsso_hces_2023/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12FA55C3-B18D-4937-BABE-02992A857F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{12FA55C3-B18D-4937-BABE-02992A857F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{801E79A6-E0AD-4BAF-B362-2E5B9C1A1BB0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4B3BEF07-B5A6-47F0-8958-68537F84A5FE}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4B3BEF07-B5A6-47F0-8958-68537F84A5FE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="hdds" sheetId="1" r:id="rId1"/>
+    <sheet name="mdd_w" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="184">
   <si>
     <t>item_code</t>
   </si>
@@ -561,6 +562,33 @@
   </si>
   <si>
     <t>misc</t>
+  </si>
+  <si>
+    <t>grains_roots_tubers</t>
+  </si>
+  <si>
+    <t>pulses</t>
+  </si>
+  <si>
+    <t>nuts_seeds</t>
+  </si>
+  <si>
+    <t>other_veg</t>
+  </si>
+  <si>
+    <t>vita_fruit_veg</t>
+  </si>
+  <si>
+    <t>green_leafy_veg</t>
+  </si>
+  <si>
+    <t>other_fruit</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>meat_poultry_fish</t>
   </si>
 </sst>
 </file>
@@ -644,9 +672,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -684,7 +712,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -790,7 +818,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -932,7 +960,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2770,4 +2798,1831 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1007B1C-E9C8-4A73-980F-04078FECD3B1}">
+  <dimension ref="A1:M163"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" t="s">
+        <v>179</v>
+      </c>
+      <c r="K1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>55</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>57</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>58</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>60</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>66</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>67</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>68</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>70</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>71</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>72</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>73</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>74</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>75</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>92</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>94</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>101</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>102</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>103</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>104</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>105</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>106</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>107</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>108</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>110</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>111</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>112</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>113</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>114</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>115</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>117</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
+        <v>118</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
+        <v>122</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
+        <v>139</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
+        <v>140</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
+        <v>141</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
+        <v>142</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
+        <v>143</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>144</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>145</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>146</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>147</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>148</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
+        <v>150</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>152</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>158</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
+        <v>160</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>161</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
+        <v>162</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
+        <v>163</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>164</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <v>165</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
+        <v>166</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
+        <v>170</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
+        <v>171</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
+        <v>172</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
+        <v>173</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
+        <v>174</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
+        <v>175</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
+        <v>178</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
+        <v>180</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A77" s="2">
+        <v>181</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A78" s="2">
+        <v>182</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A79" s="2">
+        <v>183</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A80" s="2">
+        <v>184</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A81" s="2">
+        <v>185</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
+        <v>188</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
+        <v>190</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
+        <v>191</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
+        <v>192</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A86" s="2">
+        <v>193</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A87" s="2">
+        <v>194</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A88" s="2">
+        <v>195</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A89" s="2">
+        <v>196</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A90" s="2">
+        <v>200</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A91" s="2">
+        <v>201</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A92" s="2">
+        <v>202</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A93" s="2">
+        <v>203</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A94" s="2">
+        <v>204</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A95" s="2">
+        <v>205</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A96" s="2">
+        <v>206</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A97" s="2">
+        <v>207</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A98" s="2">
+        <v>208</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A99" s="2">
+        <v>210</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A100" s="2">
+        <v>211</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A101" s="2">
+        <v>212</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A102" s="2">
+        <v>213</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A103" s="2">
+        <v>214</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A104" s="2">
+        <v>215</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A105" s="2">
+        <v>216</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A106" s="2">
+        <v>217</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A107" s="2">
+        <v>220</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A108" s="2">
+        <v>221</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A109" s="2">
+        <v>222</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A110" s="2">
+        <v>223</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A111" s="2">
+        <v>224</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A112" s="2">
+        <v>225</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A113" s="2">
+        <v>226</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A114" s="2">
+        <v>227</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A115" s="2">
+        <v>228</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A116" s="2">
+        <v>230</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A117" s="2">
+        <v>231</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A118" s="2">
+        <v>232</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A119" s="2">
+        <v>233</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A120" s="2">
+        <v>234</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A121" s="2">
+        <v>235</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A122" s="2">
+        <v>236</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A123" s="2">
+        <v>237</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A124" s="2">
+        <v>238</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A125" s="2">
+        <v>240</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A126" s="2">
+        <v>241</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A127" s="2">
+        <v>242</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A128" s="2">
+        <v>243</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A129" s="2">
+        <v>244</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A130" s="2">
+        <v>245</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A131" s="2">
+        <v>246</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A132" s="2">
+        <v>250</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A133" s="2">
+        <v>251</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A134" s="2">
+        <v>252</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A135" s="2">
+        <v>253</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A136" s="2">
+        <v>254</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A137" s="2">
+        <v>255</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A138" s="2">
+        <v>256</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A139" s="2">
+        <v>257</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A140" s="2">
+        <v>258</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A141" s="2">
+        <v>260</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A142" s="2">
+        <v>261</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A143" s="3">
+        <v>263</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A144" s="2">
+        <v>270</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A145" s="2">
+        <v>271</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A146" s="2">
+        <v>272</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A147" s="2">
+        <v>273</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A148" s="2">
+        <v>274</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A149" s="2">
+        <v>275</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A150" s="2">
+        <v>276</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A151" s="2">
+        <v>278</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A152" s="2">
+        <v>280</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A153" s="2">
+        <v>281</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A154" s="2">
+        <v>282</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A155" s="2">
+        <v>283</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A156" s="2">
+        <v>284</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A157" s="2">
+        <v>290</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A158" s="2">
+        <v>291</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A159" s="2">
+        <v>292</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A160" s="2">
+        <v>293</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A161" s="2">
+        <v>294</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A162" s="2">
+        <v>295</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A163" s="2">
+        <v>296</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>